--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD07E2E7-10AD-C540-BDE5-620BDE04D51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8EF9A0-8CA4-CA4F-B04C-42730604C6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>Documento</t>
   </si>
@@ -461,6 +461,36 @@
   </si>
   <si>
     <t>1026298117</t>
+  </si>
+  <si>
+    <t>Claudia Angélica Díaz Castiblanco</t>
+  </si>
+  <si>
+    <t>Bexy Karolina Torres Rojas</t>
+  </si>
+  <si>
+    <t>Diana Paola Daza Tinjaca</t>
+  </si>
+  <si>
+    <t>Karen Katherine Sierra Rosas</t>
+  </si>
+  <si>
+    <t>Catalina Mayorga Pajarito</t>
+  </si>
+  <si>
+    <t>52528848</t>
+  </si>
+  <si>
+    <t>1499908</t>
+  </si>
+  <si>
+    <t>1023928125</t>
+  </si>
+  <si>
+    <t>1012457979</t>
+  </si>
+  <si>
+    <t>1031172293</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -1565,36 +1595,76 @@
         <v>139</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
+    <row r="71" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B59" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}"/>
-  <conditionalFormatting sqref="A2:A70">
-    <cfRule type="duplicateValues" dxfId="11" priority="38"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A15">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A39">
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A39">
-    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A40:A70">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A2:A75">
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:A75">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
